--- a/output/stock_quant_scores/RACE_income_df.xlsx
+++ b/output/stock_quant_scores/RACE_income_df.xlsx
@@ -1298,7 +1298,9 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>1065900000</v>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1309,10 +1311,14 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>4.5</v>
+      </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
+      <c r="Y6" t="n">
+        <v>830767000</v>
+      </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
@@ -1336,9 +1342,13 @@
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
+      <c r="AU6" t="n">
+        <v>2190281000</v>
+      </c>
       <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
+      <c r="AW6" t="n">
+        <v>4270894000</v>
+      </c>
       <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
